--- a/dietaryindex_SCORING_ALGORITHM.xlsx
+++ b/dietaryindex_SCORING_ALGORITHM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10917"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Desktop/Emory University - Ph.D./dietaryindex_package/dietaryindex/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD082BF-0BB8-A645-9F63-D0CEAAAF16CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004C4113-7E5E-204D-BA21-CE5A71DB253D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="500" windowWidth="33460" windowHeight="19420" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="500" windowWidth="33460" windowHeight="19420" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HEI2020" sheetId="18" r:id="rId1"/>
@@ -361,12 +361,6 @@
   </si>
   <si>
     <t>&lt; Median</t>
-  </si>
-  <si>
-    <t>&lt; 10 or &gt;25 g/d</t>
-  </si>
-  <si>
-    <t>10-25 g/day</t>
   </si>
   <si>
     <t>Whole Fruit + Fruit juice</t>
@@ -1846,6 +1840,12 @@
   </si>
   <si>
     <t>Components of the Dietary Index for Gut Microbiota (DI-GM) identified based on the systematic review.</t>
+  </si>
+  <si>
+    <t>&lt; 5 or &gt;15 g/d</t>
+  </si>
+  <si>
+    <t>5-15 g/day</t>
   </si>
 </sst>
 </file>
@@ -2697,6 +2697,18 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2714,24 +2726,153 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2756,152 +2897,11 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3263,16 +3263,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="111" t="s">
-        <v>445</v>
-      </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
+      <c r="A1" s="115" t="s">
+        <v>443</v>
+      </c>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3285,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -3297,7 +3297,7 @@
         <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -3310,13 +3310,13 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="110" t="s">
-        <v>255</v>
+      <c r="H3" s="114" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>16</v>
@@ -3336,11 +3336,11 @@
       <c r="G4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="110"/>
+      <c r="H4" s="114"/>
     </row>
     <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>18</v>
@@ -3360,11 +3360,11 @@
       <c r="G5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="110"/>
+      <c r="H5" s="114"/>
     </row>
     <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>19</v>
@@ -3384,11 +3384,11 @@
       <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="110"/>
+      <c r="H6" s="114"/>
     </row>
     <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>20</v>
@@ -3408,17 +3408,17 @@
       <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="110"/>
+      <c r="H7" s="114"/>
     </row>
     <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D8" s="8">
         <v>0</v>
@@ -3432,17 +3432,17 @@
       <c r="G8" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="110"/>
+      <c r="H8" s="114"/>
     </row>
     <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D9" s="8">
         <v>0</v>
@@ -3456,11 +3456,11 @@
       <c r="G9" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="110"/>
+      <c r="H9" s="114"/>
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>6</v>
@@ -3480,7 +3480,7 @@
       <c r="G10" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="110"/>
+      <c r="H10" s="114"/>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -3504,7 +3504,7 @@
       <c r="G11" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="110"/>
+      <c r="H11" s="114"/>
     </row>
     <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -3526,9 +3526,9 @@
         <v>84</v>
       </c>
       <c r="G12" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" s="110"/>
+        <v>132</v>
+      </c>
+      <c r="H12" s="114"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
@@ -3540,11 +3540,11 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="110"/>
+      <c r="H13" s="114"/>
     </row>
     <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>9</v>
@@ -3564,7 +3564,7 @@
       <c r="G14" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="110"/>
+      <c r="H14" s="114"/>
     </row>
     <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -3588,17 +3588,17 @@
       <c r="G15" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="110"/>
+      <c r="H15" s="114"/>
     </row>
     <row r="16" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D16" s="8">
         <v>0</v>
@@ -3612,17 +3612,17 @@
       <c r="G16" t="s">
         <v>41</v>
       </c>
-      <c r="H16" s="110"/>
+      <c r="H16" s="114"/>
     </row>
     <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D17" s="8">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       <c r="G17" t="s">
         <v>42</v>
       </c>
-      <c r="H17" s="110"/>
+      <c r="H17" s="114"/>
     </row>
     <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="C19" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3654,25 +3654,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="A23" s="111" t="s">
-        <v>446</v>
-      </c>
-      <c r="B23" s="111"/>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
+      <c r="A23" s="115" t="s">
+        <v>444</v>
+      </c>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="115"/>
     </row>
     <row r="24" spans="1:8" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -3685,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>3</v>
@@ -3697,7 +3697,7 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -3710,13 +3710,13 @@
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
-      <c r="H25" s="110" t="s">
-        <v>255</v>
+      <c r="H25" s="114" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>16</v>
@@ -3731,16 +3731,16 @@
         <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="G26" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="110"/>
+      <c r="H26" s="114"/>
     </row>
     <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>18</v>
@@ -3755,16 +3755,16 @@
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G27" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="110"/>
+      <c r="H27" s="114"/>
     </row>
     <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>19</v>
@@ -3779,16 +3779,16 @@
         <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G28" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="110"/>
+      <c r="H28" s="114"/>
     </row>
     <row r="29" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>20</v>
@@ -3803,22 +3803,22 @@
         <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G29" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="110"/>
+      <c r="H29" s="114"/>
     </row>
     <row r="30" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D30" s="8">
         <v>0</v>
@@ -3827,22 +3827,22 @@
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G30" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="110"/>
+      <c r="H30" s="114"/>
     </row>
     <row r="31" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D31" s="8">
         <v>0</v>
@@ -3851,16 +3851,16 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G31" t="s">
         <v>39</v>
       </c>
-      <c r="H31" s="110"/>
+      <c r="H31" s="114"/>
     </row>
     <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>6</v>
@@ -3880,7 +3880,7 @@
       <c r="G32" t="s">
         <v>37</v>
       </c>
-      <c r="H32" s="110"/>
+      <c r="H32" s="114"/>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
@@ -3899,12 +3899,12 @@
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G33" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="110"/>
+      <c r="H33" s="114"/>
     </row>
     <row r="34" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
@@ -3926,9 +3926,9 @@
         <v>66</v>
       </c>
       <c r="G34" t="s">
-        <v>453</v>
-      </c>
-      <c r="H34" s="110"/>
+        <v>451</v>
+      </c>
+      <c r="H34" s="114"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
@@ -3940,11 +3940,11 @@
       <c r="E35" s="19"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
-      <c r="H35" s="110"/>
+      <c r="H35" s="114"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>9</v>
@@ -3959,12 +3959,12 @@
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G36" t="s">
-        <v>455</v>
-      </c>
-      <c r="H36" s="110"/>
+        <v>453</v>
+      </c>
+      <c r="H36" s="114"/>
     </row>
     <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -3986,19 +3986,19 @@
         <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>456</v>
-      </c>
-      <c r="H37" s="110"/>
+        <v>454</v>
+      </c>
+      <c r="H37" s="114"/>
     </row>
     <row r="38" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D38" s="8">
         <v>0</v>
@@ -4007,22 +4007,22 @@
         <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G38" t="s">
-        <v>458</v>
-      </c>
-      <c r="H38" s="110"/>
+        <v>456</v>
+      </c>
+      <c r="H38" s="114"/>
     </row>
     <row r="39" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D39" s="8">
         <v>0</v>
@@ -4031,19 +4031,19 @@
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G39" t="s">
-        <v>460</v>
-      </c>
-      <c r="H39" s="110"/>
+        <v>458</v>
+      </c>
+      <c r="H39" s="114"/>
     </row>
     <row r="40" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="9"/>
     </row>
     <row r="41" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="C41" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D41" s="9">
         <v>0</v>
@@ -4054,12 +4054,12 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -4094,67 +4094,67 @@
   <sheetData>
     <row r="1" spans="1:25" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>144</v>
-      </c>
       <c r="E1" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="K1" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="L1" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="L1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="O1" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>238</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="U1" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="U1" s="9" t="s">
-        <v>199</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="48" x14ac:dyDescent="0.2">
@@ -4177,37 +4177,37 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2" t="s">
+        <v>192</v>
+      </c>
+      <c r="M2" t="s">
+        <v>193</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="M2" t="s">
-        <v>195</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>196</v>
-      </c>
       <c r="O2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="T2">
         <v>100</v>
@@ -4216,7 +4216,7 @@
         <v>7.98</v>
       </c>
       <c r="W2" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="X2">
         <v>-8.8699999999999992</v>
@@ -4227,10 +4227,10 @@
     </row>
     <row r="3" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C3">
         <v>0.106</v>
@@ -4245,31 +4245,31 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H3" t="s">
-        <v>195</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3" t="s">
+        <v>192</v>
+      </c>
+      <c r="M3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="T3">
         <v>90</v>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="4" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C4">
         <v>-0.36499999999999999</v>
@@ -4298,25 +4298,25 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H4" t="s">
-        <v>195</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K4">
         <v>2</v>
       </c>
       <c r="L4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M4" t="s">
+        <v>193</v>
+      </c>
+      <c r="N4" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M4" t="s">
-        <v>195</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="T4">
         <v>75</v>
@@ -4327,10 +4327,10 @@
     </row>
     <row r="5" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C5">
         <v>-0.58399999999999996</v>
@@ -4345,25 +4345,25 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H5" t="s">
+        <v>193</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K5">
         <v>2</v>
       </c>
       <c r="L5" t="s">
+        <v>192</v>
+      </c>
+      <c r="M5" t="s">
+        <v>193</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M5" t="s">
-        <v>195</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="T5">
         <v>50</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="6" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -4392,25 +4392,25 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" t="s">
+        <v>193</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K6">
         <v>2</v>
       </c>
       <c r="L6" t="s">
+        <v>192</v>
+      </c>
+      <c r="M6" t="s">
+        <v>193</v>
+      </c>
+      <c r="N6" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M6" t="s">
-        <v>195</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="T6">
         <v>25</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="7" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -4439,25 +4439,25 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H7" t="s">
-        <v>195</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K7">
         <v>2</v>
       </c>
       <c r="L7" t="s">
+        <v>192</v>
+      </c>
+      <c r="M7" t="s">
+        <v>193</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M7" t="s">
-        <v>195</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="8" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C8">
         <v>0.11</v>
@@ -4486,25 +4486,25 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
+        <v>192</v>
+      </c>
+      <c r="H8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K8">
         <v>2</v>
       </c>
       <c r="L8" t="s">
+        <v>192</v>
+      </c>
+      <c r="M8" t="s">
+        <v>193</v>
+      </c>
+      <c r="N8" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M8" t="s">
-        <v>195</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -4515,10 +4515,10 @@
     </row>
     <row r="9" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C9">
         <v>0.18</v>
@@ -4533,33 +4533,33 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H9" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H9" t="s">
-        <v>195</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K9">
         <v>2</v>
       </c>
       <c r="L9" t="s">
+        <v>192</v>
+      </c>
+      <c r="M9" t="s">
+        <v>193</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M9" t="s">
-        <v>195</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C10">
         <v>-0.14000000000000001</v>
@@ -4574,30 +4574,30 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
+        <v>192</v>
+      </c>
+      <c r="H10" t="s">
+        <v>193</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H10" t="s">
-        <v>195</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K10">
         <v>2</v>
       </c>
       <c r="L10" t="s">
+        <v>192</v>
+      </c>
+      <c r="M10" t="s">
+        <v>193</v>
+      </c>
+      <c r="N10" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M10" t="s">
-        <v>195</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
@@ -4615,30 +4615,30 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H11" t="s">
-        <v>195</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K11">
         <v>2</v>
       </c>
       <c r="L11" t="s">
+        <v>192</v>
+      </c>
+      <c r="M11" t="s">
+        <v>193</v>
+      </c>
+      <c r="N11" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M11" t="s">
-        <v>195</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -4656,33 +4656,33 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H12" t="s">
+        <v>193</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H12" t="s">
-        <v>195</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K12">
         <v>2</v>
       </c>
       <c r="L12" t="s">
+        <v>192</v>
+      </c>
+      <c r="M12" t="s">
+        <v>193</v>
+      </c>
+      <c r="N12" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M12" t="s">
-        <v>195</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C13">
         <v>-0.19</v>
@@ -4697,30 +4697,30 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H13" t="s">
+        <v>193</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H13" t="s">
-        <v>195</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K13">
         <v>2</v>
       </c>
       <c r="L13" t="s">
+        <v>192</v>
+      </c>
+      <c r="M13" t="s">
+        <v>193</v>
+      </c>
+      <c r="N13" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M13" t="s">
-        <v>195</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -4738,30 +4738,30 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
+        <v>192</v>
+      </c>
+      <c r="H14" t="s">
+        <v>193</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H14" t="s">
-        <v>195</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K14">
         <v>2</v>
       </c>
       <c r="L14" t="s">
+        <v>192</v>
+      </c>
+      <c r="M14" t="s">
+        <v>193</v>
+      </c>
+      <c r="N14" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M14" t="s">
-        <v>195</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
@@ -4779,25 +4779,25 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
+        <v>192</v>
+      </c>
+      <c r="H15" t="s">
+        <v>193</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H15" t="s">
-        <v>195</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K15">
         <v>2</v>
       </c>
       <c r="L15" t="s">
+        <v>192</v>
+      </c>
+      <c r="M15" t="s">
+        <v>193</v>
+      </c>
+      <c r="N15" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M15" t="s">
-        <v>195</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="32" x14ac:dyDescent="0.2">
@@ -4805,7 +4805,7 @@
         <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C16">
         <v>3.2000000000000001E-2</v>
@@ -4820,33 +4820,33 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
+        <v>192</v>
+      </c>
+      <c r="H16" t="s">
+        <v>193</v>
+      </c>
+      <c r="I16" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H16" t="s">
-        <v>195</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K16">
         <v>2</v>
       </c>
       <c r="L16" t="s">
+        <v>192</v>
+      </c>
+      <c r="M16" t="s">
+        <v>193</v>
+      </c>
+      <c r="N16" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C17">
         <v>-0.48399999999999999</v>
@@ -4861,30 +4861,30 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H17" t="s">
-        <v>195</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K17">
         <v>2</v>
       </c>
       <c r="L17" t="s">
+        <v>192</v>
+      </c>
+      <c r="M17" t="s">
+        <v>193</v>
+      </c>
+      <c r="N17" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M17" t="s">
-        <v>195</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
@@ -4902,33 +4902,33 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
+        <v>192</v>
+      </c>
+      <c r="H18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H18" t="s">
-        <v>195</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K18">
         <v>2</v>
       </c>
       <c r="L18" t="s">
+        <v>192</v>
+      </c>
+      <c r="M18" t="s">
+        <v>193</v>
+      </c>
+      <c r="N18" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M18" t="s">
-        <v>195</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C19">
         <v>-0.246</v>
@@ -4943,30 +4943,30 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
+        <v>192</v>
+      </c>
+      <c r="H19" t="s">
+        <v>193</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H19" t="s">
-        <v>195</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K19">
         <v>2</v>
       </c>
       <c r="L19" t="s">
+        <v>192</v>
+      </c>
+      <c r="M19" t="s">
+        <v>193</v>
+      </c>
+      <c r="N19" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M19" t="s">
-        <v>195</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
@@ -4984,30 +4984,30 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
+        <v>192</v>
+      </c>
+      <c r="H20" t="s">
+        <v>193</v>
+      </c>
+      <c r="I20" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H20" t="s">
-        <v>195</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K20">
         <v>2</v>
       </c>
       <c r="L20" t="s">
+        <v>192</v>
+      </c>
+      <c r="M20" t="s">
+        <v>193</v>
+      </c>
+      <c r="N20" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M20" t="s">
-        <v>195</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
@@ -5025,30 +5025,30 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
+        <v>192</v>
+      </c>
+      <c r="H21" t="s">
+        <v>193</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H21" t="s">
-        <v>195</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K21">
         <v>2</v>
       </c>
       <c r="L21" t="s">
+        <v>192</v>
+      </c>
+      <c r="M21" t="s">
+        <v>193</v>
+      </c>
+      <c r="N21" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M21" t="s">
-        <v>195</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
@@ -5066,30 +5066,30 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
+        <v>192</v>
+      </c>
+      <c r="H22" t="s">
+        <v>193</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H22" t="s">
-        <v>195</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K22">
         <v>2</v>
       </c>
       <c r="L22" t="s">
+        <v>192</v>
+      </c>
+      <c r="M22" t="s">
+        <v>193</v>
+      </c>
+      <c r="N22" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M22" t="s">
-        <v>195</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
@@ -5107,25 +5107,25 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
+        <v>192</v>
+      </c>
+      <c r="H23" t="s">
+        <v>193</v>
+      </c>
+      <c r="I23" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H23" t="s">
-        <v>195</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K23">
         <v>2</v>
       </c>
       <c r="L23" t="s">
+        <v>192</v>
+      </c>
+      <c r="M23" t="s">
+        <v>193</v>
+      </c>
+      <c r="N23" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M23" t="s">
-        <v>195</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="32" x14ac:dyDescent="0.2">
@@ -5148,33 +5148,33 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
+        <v>192</v>
+      </c>
+      <c r="H24" t="s">
+        <v>193</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H24" t="s">
-        <v>195</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K24">
         <v>2</v>
       </c>
       <c r="L24" t="s">
+        <v>192</v>
+      </c>
+      <c r="M24" t="s">
+        <v>193</v>
+      </c>
+      <c r="N24" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M24" t="s">
-        <v>195</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C25">
         <v>-6.8000000000000005E-2</v>
@@ -5189,30 +5189,30 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
+        <v>192</v>
+      </c>
+      <c r="H25" t="s">
+        <v>193</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H25" t="s">
-        <v>195</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K25">
         <v>2</v>
       </c>
       <c r="L25" t="s">
+        <v>192</v>
+      </c>
+      <c r="M25" t="s">
+        <v>193</v>
+      </c>
+      <c r="N25" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M25" t="s">
-        <v>195</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
@@ -5230,30 +5230,30 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" t="s">
+        <v>193</v>
+      </c>
+      <c r="I26" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H26" t="s">
-        <v>195</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K26">
         <v>2</v>
       </c>
       <c r="L26" t="s">
+        <v>192</v>
+      </c>
+      <c r="M26" t="s">
+        <v>193</v>
+      </c>
+      <c r="N26" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M26" t="s">
-        <v>195</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
@@ -5271,33 +5271,33 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
+        <v>192</v>
+      </c>
+      <c r="H27" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H27" t="s">
-        <v>195</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K27">
         <v>2</v>
       </c>
       <c r="L27" t="s">
+        <v>192</v>
+      </c>
+      <c r="M27" t="s">
+        <v>193</v>
+      </c>
+      <c r="N27" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M27" t="s">
-        <v>195</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C28">
         <v>-0.191</v>
@@ -5312,33 +5312,33 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
+        <v>192</v>
+      </c>
+      <c r="H28" t="s">
+        <v>193</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H28" t="s">
-        <v>195</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K28">
         <v>2</v>
       </c>
       <c r="L28" t="s">
+        <v>192</v>
+      </c>
+      <c r="M28" t="s">
+        <v>193</v>
+      </c>
+      <c r="N28" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M28" t="s">
-        <v>195</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C29">
         <v>-9.8000000000000004E-2</v>
@@ -5353,30 +5353,30 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
+        <v>192</v>
+      </c>
+      <c r="H29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I29" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H29" t="s">
-        <v>195</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K29">
         <v>2</v>
       </c>
       <c r="L29" t="s">
+        <v>192</v>
+      </c>
+      <c r="M29" t="s">
+        <v>193</v>
+      </c>
+      <c r="N29" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M29" t="s">
-        <v>195</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
@@ -5394,33 +5394,33 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
+        <v>192</v>
+      </c>
+      <c r="H30" t="s">
+        <v>193</v>
+      </c>
+      <c r="I30" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H30" t="s">
-        <v>195</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K30">
         <v>2</v>
       </c>
       <c r="L30" t="s">
+        <v>192</v>
+      </c>
+      <c r="M30" t="s">
+        <v>193</v>
+      </c>
+      <c r="N30" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M30" t="s">
-        <v>195</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C31">
         <v>-0.78500000000000003</v>
@@ -5435,33 +5435,33 @@
         <v>1</v>
       </c>
       <c r="G31" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H31" t="s">
-        <v>195</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K31">
         <v>2</v>
       </c>
       <c r="L31" t="s">
+        <v>192</v>
+      </c>
+      <c r="M31" t="s">
+        <v>193</v>
+      </c>
+      <c r="N31" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M31" t="s">
-        <v>195</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C32">
         <v>-0.40100000000000002</v>
@@ -5476,33 +5476,33 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
+        <v>192</v>
+      </c>
+      <c r="H32" t="s">
+        <v>193</v>
+      </c>
+      <c r="I32" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H32" t="s">
-        <v>195</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K32">
         <v>2</v>
       </c>
       <c r="L32" t="s">
+        <v>192</v>
+      </c>
+      <c r="M32" t="s">
+        <v>193</v>
+      </c>
+      <c r="N32" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M32" t="s">
-        <v>195</v>
-      </c>
-      <c r="N32" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C33">
         <v>-0.42399999999999999</v>
@@ -5517,33 +5517,33 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
+        <v>192</v>
+      </c>
+      <c r="H33" t="s">
+        <v>193</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H33" t="s">
-        <v>195</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
+        <v>192</v>
+      </c>
+      <c r="M33" t="s">
+        <v>193</v>
+      </c>
+      <c r="N33" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M33" t="s">
-        <v>195</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C34">
         <v>-0.44600000000000001</v>
@@ -5558,33 +5558,33 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
+        <v>192</v>
+      </c>
+      <c r="H34" t="s">
+        <v>193</v>
+      </c>
+      <c r="I34" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H34" t="s">
-        <v>195</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K34">
         <v>2</v>
       </c>
       <c r="L34" t="s">
+        <v>192</v>
+      </c>
+      <c r="M34" t="s">
+        <v>193</v>
+      </c>
+      <c r="N34" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M34" t="s">
-        <v>195</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C35">
         <v>-0.41899999999999998</v>
@@ -5599,33 +5599,33 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
+        <v>192</v>
+      </c>
+      <c r="H35" t="s">
+        <v>193</v>
+      </c>
+      <c r="I35" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H35" t="s">
-        <v>195</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K35">
         <v>2</v>
       </c>
       <c r="L35" t="s">
+        <v>192</v>
+      </c>
+      <c r="M35" t="s">
+        <v>193</v>
+      </c>
+      <c r="N35" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M35" t="s">
-        <v>195</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C36">
         <v>-0.313</v>
@@ -5640,30 +5640,30 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H36" t="s">
+        <v>193</v>
+      </c>
+      <c r="I36" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H36" t="s">
-        <v>195</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K36">
         <v>2</v>
       </c>
       <c r="L36" t="s">
+        <v>192</v>
+      </c>
+      <c r="M36" t="s">
+        <v>193</v>
+      </c>
+      <c r="N36" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M36" t="s">
-        <v>195</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
@@ -5681,33 +5681,33 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
+        <v>192</v>
+      </c>
+      <c r="H37" t="s">
+        <v>193</v>
+      </c>
+      <c r="I37" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H37" t="s">
-        <v>195</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K37">
         <v>2</v>
       </c>
       <c r="L37" t="s">
+        <v>192</v>
+      </c>
+      <c r="M37" t="s">
+        <v>193</v>
+      </c>
+      <c r="N37" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M37" t="s">
-        <v>195</v>
-      </c>
-      <c r="N37" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B38" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C38">
         <v>-0.41499999999999998</v>
@@ -5722,33 +5722,33 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
+        <v>192</v>
+      </c>
+      <c r="H38" t="s">
+        <v>193</v>
+      </c>
+      <c r="I38" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H38" t="s">
-        <v>195</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K38">
         <v>2</v>
       </c>
       <c r="L38" t="s">
+        <v>192</v>
+      </c>
+      <c r="M38" t="s">
+        <v>193</v>
+      </c>
+      <c r="N38" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M38" t="s">
-        <v>195</v>
-      </c>
-      <c r="N38" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C39">
         <v>-0.61599999999999999</v>
@@ -5763,33 +5763,33 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
+        <v>192</v>
+      </c>
+      <c r="H39" t="s">
+        <v>193</v>
+      </c>
+      <c r="I39" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H39" t="s">
-        <v>195</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K39">
         <v>2</v>
       </c>
       <c r="L39" t="s">
+        <v>192</v>
+      </c>
+      <c r="M39" t="s">
+        <v>193</v>
+      </c>
+      <c r="N39" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M39" t="s">
-        <v>195</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C40">
         <v>-0.46700000000000003</v>
@@ -5804,33 +5804,33 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
+        <v>192</v>
+      </c>
+      <c r="H40" t="s">
+        <v>193</v>
+      </c>
+      <c r="I40" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H40" t="s">
-        <v>195</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K40">
         <v>2</v>
       </c>
       <c r="L40" t="s">
+        <v>192</v>
+      </c>
+      <c r="M40" t="s">
+        <v>193</v>
+      </c>
+      <c r="N40" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M40" t="s">
-        <v>195</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C41">
         <v>-0.25</v>
@@ -5845,33 +5845,33 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
+        <v>192</v>
+      </c>
+      <c r="H41" t="s">
+        <v>193</v>
+      </c>
+      <c r="I41" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H41" t="s">
-        <v>195</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K41">
         <v>2</v>
       </c>
       <c r="L41" t="s">
+        <v>192</v>
+      </c>
+      <c r="M41" t="s">
+        <v>193</v>
+      </c>
+      <c r="N41" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M41" t="s">
-        <v>195</v>
-      </c>
-      <c r="N41" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C42">
         <v>-0.13100000000000001</v>
@@ -5886,33 +5886,33 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
+        <v>192</v>
+      </c>
+      <c r="H42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I42" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H42" t="s">
-        <v>195</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K42">
         <v>2</v>
       </c>
       <c r="L42" t="s">
+        <v>192</v>
+      </c>
+      <c r="M42" t="s">
+        <v>193</v>
+      </c>
+      <c r="N42" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M42" t="s">
-        <v>195</v>
-      </c>
-      <c r="N42" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B43" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C43">
         <v>-0.59299999999999997</v>
@@ -5927,30 +5927,30 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
+        <v>192</v>
+      </c>
+      <c r="H43" t="s">
+        <v>193</v>
+      </c>
+      <c r="I43" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H43" t="s">
-        <v>195</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K43">
         <v>2</v>
       </c>
       <c r="L43" t="s">
+        <v>192</v>
+      </c>
+      <c r="M43" t="s">
+        <v>193</v>
+      </c>
+      <c r="N43" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M43" t="s">
-        <v>195</v>
-      </c>
-      <c r="N43" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B44" t="s">
         <v>15</v>
@@ -5968,33 +5968,33 @@
         <v>1</v>
       </c>
       <c r="G44" t="s">
+        <v>192</v>
+      </c>
+      <c r="H44" t="s">
+        <v>193</v>
+      </c>
+      <c r="I44" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H44" t="s">
-        <v>195</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K44">
         <v>2</v>
       </c>
       <c r="L44" t="s">
+        <v>192</v>
+      </c>
+      <c r="M44" t="s">
+        <v>193</v>
+      </c>
+      <c r="N44" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M44" t="s">
-        <v>195</v>
-      </c>
-      <c r="N44" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C45">
         <v>-0.10199999999999999</v>
@@ -6009,33 +6009,33 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
+        <v>192</v>
+      </c>
+      <c r="H45" t="s">
+        <v>193</v>
+      </c>
+      <c r="I45" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H45" t="s">
-        <v>195</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
+        <v>192</v>
+      </c>
+      <c r="M45" t="s">
+        <v>193</v>
+      </c>
+      <c r="N45" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M45" t="s">
-        <v>195</v>
-      </c>
-      <c r="N45" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" t="s">
         <v>185</v>
-      </c>
-      <c r="B46" t="s">
-        <v>187</v>
       </c>
       <c r="C46">
         <v>-1.2999999999999999E-2</v>
@@ -6050,35 +6050,35 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
+        <v>192</v>
+      </c>
+      <c r="H46" t="s">
+        <v>193</v>
+      </c>
+      <c r="I46" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="H46" t="s">
-        <v>195</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
+        <v>192</v>
+      </c>
+      <c r="M46" t="s">
+        <v>193</v>
+      </c>
+      <c r="N46" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="M46" t="s">
-        <v>195</v>
-      </c>
-      <c r="N46" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -6109,19 +6109,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -6139,10 +6139,10 @@
         <v>52</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D4" s="8">
         <v>0</v>
@@ -6151,16 +6151,16 @@
         <v>0.75</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="22"/>
       <c r="B5" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D5" s="8">
         <v>0</v>
@@ -6169,18 +6169,18 @@
         <v>0.75</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>212</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -6189,16 +6189,16 @@
         <v>0.75</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="22"/>
       <c r="B7" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D7" s="8">
         <v>0</v>
@@ -6207,7 +6207,7 @@
         <v>0.75</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6215,10 +6215,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D8" s="8">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6238,7 +6238,7 @@
         <v>87</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D9" s="8">
         <v>0</v>
@@ -6247,18 +6247,18 @@
         <v>3</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>225</v>
       </c>
       <c r="D10" s="8">
         <v>0</v>
@@ -6267,24 +6267,24 @@
         <v>1.5</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="F11" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>219</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>221</v>
       </c>
       <c r="D12" s="8">
         <v>0</v>
@@ -6293,7 +6293,7 @@
         <v>1.5</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -6301,7 +6301,7 @@
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -6312,12 +6312,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
@@ -6350,19 +6350,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -6380,10 +6380,10 @@
         <v>52</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D4" s="8">
         <v>0</v>
@@ -6392,16 +6392,16 @@
         <v>0.75</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="22"/>
       <c r="B5" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D5" s="8">
         <v>0</v>
@@ -6410,18 +6410,18 @@
         <v>0.75</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>212</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -6430,16 +6430,16 @@
         <v>0.75</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="22"/>
       <c r="B7" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D7" s="8">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         <v>0.75</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
@@ -6456,10 +6456,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D8" s="8">
         <v>0</v>
@@ -6468,7 +6468,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6479,7 +6479,7 @@
         <v>87</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D9" s="8">
         <v>0</v>
@@ -6488,18 +6488,18 @@
         <v>3</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D10" s="8">
         <v>0</v>
@@ -6508,24 +6508,24 @@
         <v>1.5</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="F11" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="1" customFormat="1" ht="128" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>219</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>221</v>
       </c>
       <c r="D12" s="8">
         <v>0</v>
@@ -6534,7 +6534,7 @@
         <v>1.5</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -6544,7 +6544,7 @@
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -6555,12 +6555,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
@@ -6591,536 +6591,536 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="170" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1" s="173" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="77" t="s">
-        <v>311</v>
-      </c>
-      <c r="C1" s="126" t="s">
-        <v>312</v>
-      </c>
-      <c r="D1" s="127"/>
+      <c r="D1" s="174"/>
       <c r="E1" s="23"/>
       <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" s="25" customFormat="1" ht="31" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="124"/>
+      <c r="A2" s="171"/>
       <c r="B2" s="78" t="s">
-        <v>313</v>
-      </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="129"/>
+        <v>311</v>
+      </c>
+      <c r="C2" s="175"/>
+      <c r="D2" s="176"/>
       <c r="E2" s="23"/>
       <c r="F2" s="24"/>
     </row>
     <row r="3" spans="1:6" s="29" customFormat="1" ht="49" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="125"/>
+      <c r="A3" s="172"/>
       <c r="B3" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="E3" s="103" t="s">
         <v>315</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="F3" s="103" t="s">
         <v>316</v>
       </c>
-      <c r="E3" s="103" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="177" t="s">
         <v>317</v>
       </c>
-      <c r="F3" s="103" t="s">
+      <c r="B4" s="178" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="130" t="s">
+      <c r="C4" s="145">
+        <v>0</v>
+      </c>
+      <c r="D4" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="E4" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="134">
-        <v>0</v>
-      </c>
-      <c r="D4" s="30" t="s">
+      <c r="F4" s="32"/>
+    </row>
+    <row r="5" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="169"/>
+      <c r="B5" s="179"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="33" t="s">
         <v>321</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="F4" s="32"/>
-    </row>
-    <row r="5" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="131"/>
-      <c r="B5" s="133"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="33" t="s">
-        <v>323</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="32"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="117" t="s">
+      <c r="A6" s="125" t="s">
+        <v>322</v>
+      </c>
+      <c r="B6" s="127" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6" s="125" t="s">
         <v>324</v>
       </c>
-      <c r="B6" s="119" t="s">
+      <c r="D6" s="165" t="s">
         <v>325</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="E6" s="92" t="s">
         <v>326</v>
-      </c>
-      <c r="D6" s="121" t="s">
-        <v>327</v>
-      </c>
-      <c r="E6" s="92" t="s">
-        <v>328</v>
       </c>
       <c r="F6" s="93">
         <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="118"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="122"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="153"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="166"/>
       <c r="E7" s="94" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F7" s="95">
         <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="118"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="122"/>
+      <c r="A8" s="152"/>
+      <c r="B8" s="153"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="166"/>
       <c r="E8" s="94" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F8" s="95">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="136" t="s">
+      <c r="A9" s="143" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" s="145" t="s">
+        <v>330</v>
+      </c>
+      <c r="C9" s="145">
+        <v>0</v>
+      </c>
+      <c r="D9" s="145" t="s">
         <v>331</v>
       </c>
-      <c r="B9" s="134" t="s">
+      <c r="E9" s="34" t="s">
         <v>332</v>
-      </c>
-      <c r="C9" s="134">
-        <v>0</v>
-      </c>
-      <c r="D9" s="134" t="s">
-        <v>333</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>334</v>
       </c>
       <c r="F9" s="35">
         <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="137"/>
-      <c r="B10" s="138"/>
-      <c r="C10" s="138"/>
-      <c r="D10" s="138"/>
+      <c r="A10" s="144"/>
+      <c r="B10" s="146"/>
+      <c r="C10" s="146"/>
+      <c r="D10" s="146"/>
       <c r="E10" s="36" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F10" s="37">
         <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="137"/>
-      <c r="B11" s="138"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
+      <c r="A11" s="144"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
       <c r="E11" s="36" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F11" s="37">
         <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="137"/>
-      <c r="B12" s="138"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="138"/>
+      <c r="A12" s="144"/>
+      <c r="B12" s="146"/>
+      <c r="C12" s="146"/>
+      <c r="D12" s="146"/>
       <c r="E12" s="36"/>
       <c r="F12" s="37"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="137"/>
-      <c r="B13" s="138"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="138"/>
+      <c r="A13" s="144"/>
+      <c r="B13" s="146"/>
+      <c r="C13" s="146"/>
+      <c r="D13" s="146"/>
       <c r="E13" s="36" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F13" s="37">
         <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="137"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
+      <c r="A14" s="144"/>
+      <c r="B14" s="146"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="146"/>
       <c r="E14" s="36" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F14" s="37">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="137"/>
-      <c r="B15" s="138"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
+      <c r="A15" s="144"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="146"/>
+      <c r="D15" s="146"/>
       <c r="E15" s="36" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F15" s="37">
         <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="137"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
+      <c r="A16" s="144"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="146"/>
       <c r="E16" s="36" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F16" s="37">
         <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="137"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
+      <c r="A17" s="144"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="146"/>
+      <c r="D17" s="146"/>
       <c r="E17" s="36" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F17" s="37">
         <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="137"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
+      <c r="A18" s="144"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="146"/>
       <c r="E18" s="36" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F18" s="37">
         <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="137"/>
-      <c r="B19" s="138"/>
-      <c r="C19" s="138"/>
-      <c r="D19" s="138"/>
+      <c r="A19" s="144"/>
+      <c r="B19" s="146"/>
+      <c r="C19" s="146"/>
+      <c r="D19" s="146"/>
       <c r="E19" s="36" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F19" s="37">
         <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="137"/>
-      <c r="B20" s="138"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
+      <c r="A20" s="144"/>
+      <c r="B20" s="146"/>
+      <c r="C20" s="146"/>
+      <c r="D20" s="146"/>
       <c r="E20" s="36" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F20" s="37">
         <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="137"/>
-      <c r="B21" s="138"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="138"/>
+      <c r="A21" s="144"/>
+      <c r="B21" s="146"/>
+      <c r="C21" s="146"/>
+      <c r="D21" s="146"/>
       <c r="E21" s="36" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F21" s="38">
         <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="137"/>
-      <c r="B22" s="138"/>
-      <c r="C22" s="138"/>
-      <c r="D22" s="138"/>
+      <c r="A22" s="144"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="146"/>
+      <c r="D22" s="146"/>
       <c r="E22" s="36" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F22" s="38">
         <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="137"/>
-      <c r="B23" s="138"/>
-      <c r="C23" s="138"/>
-      <c r="D23" s="138"/>
+      <c r="A23" s="144"/>
+      <c r="B23" s="146"/>
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
       <c r="E23" s="36" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F23" s="38">
         <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="137"/>
-      <c r="B24" s="138"/>
-      <c r="C24" s="138"/>
-      <c r="D24" s="138"/>
+      <c r="A24" s="144"/>
+      <c r="B24" s="146"/>
+      <c r="C24" s="146"/>
+      <c r="D24" s="146"/>
       <c r="E24" s="36" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F24" s="37">
         <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="137"/>
-      <c r="B25" s="138"/>
-      <c r="C25" s="138"/>
-      <c r="D25" s="138"/>
+      <c r="A25" s="144"/>
+      <c r="B25" s="146"/>
+      <c r="C25" s="146"/>
+      <c r="D25" s="146"/>
       <c r="E25" s="36" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F25" s="37">
         <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="137"/>
-      <c r="B26" s="138"/>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
+      <c r="A26" s="144"/>
+      <c r="B26" s="146"/>
+      <c r="C26" s="146"/>
+      <c r="D26" s="146"/>
       <c r="E26" s="36" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F26" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="137"/>
-      <c r="B27" s="138"/>
-      <c r="C27" s="138"/>
-      <c r="D27" s="138"/>
+      <c r="A27" s="144"/>
+      <c r="B27" s="146"/>
+      <c r="C27" s="146"/>
+      <c r="D27" s="146"/>
       <c r="E27" s="36" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F27" s="37">
         <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="137"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
+      <c r="A28" s="144"/>
+      <c r="B28" s="146"/>
+      <c r="C28" s="146"/>
+      <c r="D28" s="146"/>
       <c r="E28" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F28" s="37">
         <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="137"/>
-      <c r="B29" s="138"/>
-      <c r="C29" s="138"/>
-      <c r="D29" s="138"/>
+      <c r="A29" s="144"/>
+      <c r="B29" s="146"/>
+      <c r="C29" s="146"/>
+      <c r="D29" s="146"/>
       <c r="E29" s="36" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F29" s="37">
         <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="137"/>
-      <c r="B30" s="138"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="138"/>
+      <c r="A30" s="144"/>
+      <c r="B30" s="146"/>
+      <c r="C30" s="146"/>
+      <c r="D30" s="146"/>
       <c r="E30" s="36" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F30" s="37">
         <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="137"/>
-      <c r="B31" s="138"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="138"/>
+      <c r="A31" s="144"/>
+      <c r="B31" s="146"/>
+      <c r="C31" s="146"/>
+      <c r="D31" s="146"/>
       <c r="E31" s="36" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F31" s="37">
         <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="137"/>
-      <c r="B32" s="138"/>
-      <c r="C32" s="138"/>
-      <c r="D32" s="138"/>
+      <c r="A32" s="144"/>
+      <c r="B32" s="146"/>
+      <c r="C32" s="146"/>
+      <c r="D32" s="146"/>
       <c r="E32" s="36" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F32" s="37">
         <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="137"/>
-      <c r="B33" s="138"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="138"/>
+      <c r="A33" s="144"/>
+      <c r="B33" s="146"/>
+      <c r="C33" s="146"/>
+      <c r="D33" s="146"/>
       <c r="E33" s="36" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F33" s="38">
         <v>37.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="137"/>
-      <c r="B34" s="138"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="138"/>
+      <c r="A34" s="144"/>
+      <c r="B34" s="146"/>
+      <c r="C34" s="146"/>
+      <c r="D34" s="146"/>
       <c r="E34" s="36"/>
       <c r="F34" s="38"/>
       <c r="G34" s="8"/>
       <c r="H34" s="39"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="137"/>
-      <c r="B35" s="138"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="138"/>
+      <c r="A35" s="144"/>
+      <c r="B35" s="146"/>
+      <c r="C35" s="146"/>
+      <c r="D35" s="146"/>
       <c r="E35" s="36" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F35" s="38">
         <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="137"/>
-      <c r="B36" s="138"/>
-      <c r="C36" s="138"/>
-      <c r="D36" s="138"/>
+      <c r="A36" s="144"/>
+      <c r="B36" s="146"/>
+      <c r="C36" s="146"/>
+      <c r="D36" s="146"/>
       <c r="E36" s="36"/>
       <c r="F36" s="38"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="137"/>
-      <c r="B37" s="138"/>
-      <c r="C37" s="138"/>
-      <c r="D37" s="138"/>
+      <c r="A37" s="144"/>
+      <c r="B37" s="146"/>
+      <c r="C37" s="146"/>
+      <c r="D37" s="146"/>
       <c r="E37" s="36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F37" s="37">
         <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="137"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
+      <c r="A38" s="144"/>
+      <c r="B38" s="146"/>
+      <c r="C38" s="146"/>
+      <c r="D38" s="146"/>
       <c r="E38" s="36" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F38" s="37">
         <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="131"/>
-      <c r="B39" s="135"/>
-      <c r="C39" s="135"/>
-      <c r="D39" s="135"/>
+      <c r="A39" s="169"/>
+      <c r="B39" s="168"/>
+      <c r="C39" s="168"/>
+      <c r="D39" s="168"/>
       <c r="E39" s="40" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F39" s="41">
         <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="136" t="s">
+      <c r="A40" s="143" t="s">
+        <v>360</v>
+      </c>
+      <c r="B40" s="145" t="s">
+        <v>361</v>
+      </c>
+      <c r="C40" s="145">
+        <v>0</v>
+      </c>
+      <c r="D40" s="145" t="s">
         <v>362</v>
       </c>
-      <c r="B40" s="134" t="s">
+      <c r="E40" s="42" t="s">
         <v>363</v>
-      </c>
-      <c r="C40" s="134">
-        <v>0</v>
-      </c>
-      <c r="D40" s="134" t="s">
-        <v>364</v>
-      </c>
-      <c r="E40" s="42" t="s">
-        <v>365</v>
       </c>
       <c r="F40" s="43">
         <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="137"/>
-      <c r="B41" s="138"/>
-      <c r="C41" s="138"/>
-      <c r="D41" s="138"/>
+      <c r="A41" s="144"/>
+      <c r="B41" s="146"/>
+      <c r="C41" s="146"/>
+      <c r="D41" s="146"/>
       <c r="E41" s="44"/>
       <c r="F41" s="45"/>
     </row>
     <row r="42" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="137"/>
-      <c r="B42" s="138"/>
-      <c r="C42" s="138"/>
-      <c r="D42" s="138"/>
+      <c r="A42" s="144"/>
+      <c r="B42" s="146"/>
+      <c r="C42" s="146"/>
+      <c r="D42" s="146"/>
       <c r="E42" s="44" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F42" s="37">
         <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="137"/>
-      <c r="B43" s="138"/>
-      <c r="C43" s="138"/>
-      <c r="D43" s="138"/>
+      <c r="A43" s="144"/>
+      <c r="B43" s="146"/>
+      <c r="C43" s="146"/>
+      <c r="D43" s="146"/>
       <c r="E43" s="44" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F43" s="37">
         <v>114</v>
@@ -7128,11 +7128,11 @@
     </row>
     <row r="44" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="30"/>
-      <c r="B44" s="138"/>
-      <c r="C44" s="138"/>
-      <c r="D44" s="138"/>
+      <c r="B44" s="146"/>
+      <c r="C44" s="146"/>
+      <c r="D44" s="146"/>
       <c r="E44" s="44" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F44" s="37">
         <v>135</v>
@@ -7140,11 +7140,11 @@
     </row>
     <row r="45" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="30"/>
-      <c r="B45" s="138"/>
-      <c r="C45" s="138"/>
-      <c r="D45" s="138"/>
+      <c r="B45" s="146"/>
+      <c r="C45" s="146"/>
+      <c r="D45" s="146"/>
       <c r="E45" s="44" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F45" s="45">
         <v>100.5</v>
@@ -7152,11 +7152,11 @@
     </row>
     <row r="46" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="30"/>
-      <c r="B46" s="138"/>
-      <c r="C46" s="138"/>
-      <c r="D46" s="138"/>
+      <c r="B46" s="146"/>
+      <c r="C46" s="146"/>
+      <c r="D46" s="146"/>
       <c r="E46" s="44" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F46" s="45">
         <v>138</v>
@@ -7164,11 +7164,11 @@
     </row>
     <row r="47" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="30"/>
-      <c r="B47" s="138"/>
-      <c r="C47" s="138"/>
-      <c r="D47" s="138"/>
+      <c r="B47" s="146"/>
+      <c r="C47" s="146"/>
+      <c r="D47" s="146"/>
       <c r="E47" s="44" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F47" s="45">
         <v>166</v>
@@ -7176,11 +7176,11 @@
     </row>
     <row r="48" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="30"/>
-      <c r="B48" s="138"/>
-      <c r="C48" s="138"/>
-      <c r="D48" s="138"/>
+      <c r="B48" s="146"/>
+      <c r="C48" s="146"/>
+      <c r="D48" s="146"/>
       <c r="E48" s="44" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F48" s="45">
         <v>127.5</v>
@@ -7188,19 +7188,19 @@
     </row>
     <row r="49" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="30"/>
-      <c r="B49" s="138"/>
-      <c r="C49" s="138"/>
-      <c r="D49" s="138"/>
+      <c r="B49" s="146"/>
+      <c r="C49" s="146"/>
+      <c r="D49" s="146"/>
       <c r="E49" s="44"/>
       <c r="F49" s="45"/>
     </row>
     <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" s="30"/>
-      <c r="B50" s="138"/>
-      <c r="C50" s="138"/>
-      <c r="D50" s="138"/>
+      <c r="B50" s="146"/>
+      <c r="C50" s="146"/>
+      <c r="D50" s="146"/>
       <c r="E50" s="44" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F50" s="37">
         <v>131</v>
@@ -7208,11 +7208,11 @@
     </row>
     <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" s="30"/>
-      <c r="B51" s="138"/>
-      <c r="C51" s="138"/>
-      <c r="D51" s="138"/>
+      <c r="B51" s="146"/>
+      <c r="C51" s="146"/>
+      <c r="D51" s="146"/>
       <c r="E51" s="44" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F51" s="37">
         <v>120</v>
@@ -7220,11 +7220,11 @@
     </row>
     <row r="52" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="30"/>
-      <c r="B52" s="138"/>
-      <c r="C52" s="138"/>
-      <c r="D52" s="138"/>
+      <c r="B52" s="146"/>
+      <c r="C52" s="146"/>
+      <c r="D52" s="146"/>
       <c r="E52" s="44" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F52" s="37">
         <v>75</v>
@@ -7232,11 +7232,11 @@
     </row>
     <row r="53" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A53" s="30"/>
-      <c r="B53" s="138"/>
-      <c r="C53" s="138"/>
-      <c r="D53" s="138"/>
+      <c r="B53" s="146"/>
+      <c r="C53" s="146"/>
+      <c r="D53" s="146"/>
       <c r="E53" s="44" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F53" s="37">
         <v>73</v>
@@ -7244,11 +7244,11 @@
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" s="30"/>
-      <c r="B54" s="138"/>
-      <c r="C54" s="138"/>
-      <c r="D54" s="138"/>
+      <c r="B54" s="146"/>
+      <c r="C54" s="146"/>
+      <c r="D54" s="146"/>
       <c r="E54" s="44" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F54" s="37">
         <v>128</v>
@@ -7256,19 +7256,19 @@
     </row>
     <row r="55" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="30"/>
-      <c r="B55" s="138"/>
-      <c r="C55" s="138"/>
-      <c r="D55" s="138"/>
+      <c r="B55" s="146"/>
+      <c r="C55" s="146"/>
+      <c r="D55" s="146"/>
       <c r="E55" s="44"/>
       <c r="F55" s="37"/>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" s="30"/>
-      <c r="B56" s="138"/>
-      <c r="C56" s="138"/>
-      <c r="D56" s="138"/>
+      <c r="B56" s="146"/>
+      <c r="C56" s="146"/>
+      <c r="D56" s="146"/>
       <c r="E56" s="44" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F56" s="37">
         <v>241</v>
@@ -7276,27 +7276,27 @@
     </row>
     <row r="57" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="30"/>
-      <c r="B57" s="138"/>
-      <c r="C57" s="138"/>
-      <c r="D57" s="138"/>
+      <c r="B57" s="146"/>
+      <c r="C57" s="146"/>
+      <c r="D57" s="146"/>
       <c r="E57" s="44"/>
       <c r="F57" s="45"/>
     </row>
     <row r="58" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="138"/>
-      <c r="C58" s="138"/>
-      <c r="D58" s="138"/>
+      <c r="B58" s="146"/>
+      <c r="C58" s="146"/>
+      <c r="D58" s="146"/>
       <c r="E58" s="44"/>
       <c r="F58" s="45"/>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" s="30"/>
-      <c r="B59" s="138"/>
-      <c r="C59" s="138"/>
-      <c r="D59" s="138"/>
+      <c r="B59" s="146"/>
+      <c r="C59" s="146"/>
+      <c r="D59" s="146"/>
       <c r="E59" s="44" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F59" s="45">
         <v>128</v>
@@ -7304,11 +7304,11 @@
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="30"/>
-      <c r="B60" s="138"/>
-      <c r="C60" s="138"/>
-      <c r="D60" s="138"/>
+      <c r="B60" s="146"/>
+      <c r="C60" s="146"/>
+      <c r="D60" s="146"/>
       <c r="E60" s="44" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F60" s="45">
         <v>127</v>
@@ -7316,11 +7316,11 @@
     </row>
     <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A61" s="30"/>
-      <c r="B61" s="138"/>
-      <c r="C61" s="138"/>
-      <c r="D61" s="138"/>
+      <c r="B61" s="146"/>
+      <c r="C61" s="146"/>
+      <c r="D61" s="146"/>
       <c r="E61" s="44" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F61" s="45">
         <v>128</v>
@@ -7328,502 +7328,502 @@
     </row>
     <row r="62" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="138"/>
-      <c r="C62" s="138"/>
-      <c r="D62" s="138"/>
+      <c r="B62" s="146"/>
+      <c r="C62" s="146"/>
+      <c r="D62" s="146"/>
       <c r="E62" s="44"/>
       <c r="F62" s="45"/>
     </row>
     <row r="63" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="30"/>
-      <c r="B63" s="138"/>
-      <c r="C63" s="138"/>
-      <c r="D63" s="138"/>
+      <c r="B63" s="146"/>
+      <c r="C63" s="146"/>
+      <c r="D63" s="146"/>
       <c r="E63" s="44"/>
       <c r="F63" s="45"/>
     </row>
     <row r="64" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="30"/>
-      <c r="B64" s="135"/>
-      <c r="C64" s="135"/>
-      <c r="D64" s="135"/>
+      <c r="B64" s="168"/>
+      <c r="C64" s="168"/>
+      <c r="D64" s="168"/>
       <c r="E64" s="46"/>
       <c r="F64" s="47"/>
     </row>
     <row r="65" spans="1:6" s="48" customFormat="1" ht="149.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="79" t="s">
+        <v>380</v>
+      </c>
+      <c r="B65" s="80" t="s">
+        <v>381</v>
+      </c>
+      <c r="C65" s="80" t="s">
         <v>382</v>
       </c>
-      <c r="B65" s="80" t="s">
+      <c r="D65" s="91" t="s">
         <v>383</v>
       </c>
-      <c r="C65" s="80" t="s">
+      <c r="E65" s="160" t="s">
         <v>384</v>
       </c>
-      <c r="D65" s="91" t="s">
+      <c r="F65" s="161"/>
+    </row>
+    <row r="66" spans="1:6" ht="29.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="125" t="s">
         <v>385</v>
       </c>
-      <c r="E65" s="139" t="s">
+      <c r="B66" s="127" t="s">
         <v>386</v>
       </c>
-      <c r="F65" s="140"/>
-    </row>
-    <row r="66" spans="1:6" ht="29.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="117" t="s">
+      <c r="C66" s="162" t="s">
         <v>387</v>
       </c>
-      <c r="B66" s="119" t="s">
+      <c r="D66" s="165" t="s">
         <v>388</v>
       </c>
-      <c r="C66" s="143" t="s">
+      <c r="E66" s="49" t="s">
         <v>389</v>
-      </c>
-      <c r="D66" s="121" t="s">
-        <v>390</v>
-      </c>
-      <c r="E66" s="49" t="s">
-        <v>391</v>
       </c>
       <c r="F66" s="50">
         <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A67" s="118"/>
-      <c r="B67" s="120"/>
-      <c r="C67" s="144"/>
-      <c r="D67" s="122"/>
+      <c r="A67" s="152"/>
+      <c r="B67" s="153"/>
+      <c r="C67" s="163"/>
+      <c r="D67" s="166"/>
       <c r="E67" s="51"/>
       <c r="F67" s="52"/>
     </row>
     <row r="68" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="118"/>
-      <c r="B68" s="120"/>
-      <c r="C68" s="144"/>
-      <c r="D68" s="122"/>
+      <c r="A68" s="152"/>
+      <c r="B68" s="153"/>
+      <c r="C68" s="163"/>
+      <c r="D68" s="166"/>
       <c r="E68" s="51" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F68" s="52">
         <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" s="118"/>
-      <c r="B69" s="120"/>
-      <c r="C69" s="144"/>
-      <c r="D69" s="122"/>
+      <c r="A69" s="152"/>
+      <c r="B69" s="153"/>
+      <c r="C69" s="163"/>
+      <c r="D69" s="166"/>
       <c r="E69" s="51"/>
       <c r="F69" s="52"/>
     </row>
     <row r="70" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A70" s="118"/>
-      <c r="B70" s="120"/>
-      <c r="C70" s="144"/>
-      <c r="D70" s="122"/>
+      <c r="A70" s="152"/>
+      <c r="B70" s="153"/>
+      <c r="C70" s="163"/>
+      <c r="D70" s="166"/>
       <c r="E70" s="51" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F70" s="52">
         <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A71" s="118"/>
-      <c r="B71" s="120"/>
-      <c r="C71" s="144"/>
-      <c r="D71" s="122"/>
+      <c r="A71" s="152"/>
+      <c r="B71" s="153"/>
+      <c r="C71" s="163"/>
+      <c r="D71" s="166"/>
       <c r="E71" s="51" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F71" s="52">
         <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A72" s="118"/>
-      <c r="B72" s="120"/>
-      <c r="C72" s="144"/>
-      <c r="D72" s="122"/>
+      <c r="A72" s="152"/>
+      <c r="B72" s="153"/>
+      <c r="C72" s="163"/>
+      <c r="D72" s="166"/>
       <c r="E72" s="51"/>
       <c r="F72" s="52"/>
     </row>
     <row r="73" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A73" s="118"/>
-      <c r="B73" s="120"/>
-      <c r="C73" s="144"/>
-      <c r="D73" s="122"/>
+      <c r="A73" s="152"/>
+      <c r="B73" s="153"/>
+      <c r="C73" s="163"/>
+      <c r="D73" s="166"/>
       <c r="E73" s="51" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F73" s="52">
         <v>85.4</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A74" s="118"/>
-      <c r="B74" s="120"/>
-      <c r="C74" s="144"/>
-      <c r="D74" s="122"/>
+      <c r="A74" s="152"/>
+      <c r="B74" s="153"/>
+      <c r="C74" s="163"/>
+      <c r="D74" s="166"/>
       <c r="E74" s="51"/>
       <c r="F74" s="52"/>
     </row>
     <row r="75" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="141"/>
-      <c r="B75" s="142"/>
-      <c r="C75" s="145"/>
-      <c r="D75" s="146"/>
+      <c r="A75" s="126"/>
+      <c r="B75" s="128"/>
+      <c r="C75" s="164"/>
+      <c r="D75" s="167"/>
       <c r="E75" s="53" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F75" s="54">
         <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="117" t="s">
+      <c r="A76" s="125" t="s">
+        <v>395</v>
+      </c>
+      <c r="B76" s="127" t="s">
+        <v>396</v>
+      </c>
+      <c r="C76" s="157" t="s">
+        <v>387</v>
+      </c>
+      <c r="D76" s="154" t="s">
         <v>397</v>
-      </c>
-      <c r="B76" s="119" t="s">
-        <v>398</v>
-      </c>
-      <c r="C76" s="150" t="s">
-        <v>389</v>
-      </c>
-      <c r="D76" s="147" t="s">
-        <v>399</v>
       </c>
       <c r="E76" s="81"/>
       <c r="F76" s="82"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="118"/>
-      <c r="B77" s="120"/>
-      <c r="C77" s="151"/>
-      <c r="D77" s="148"/>
+      <c r="A77" s="152"/>
+      <c r="B77" s="153"/>
+      <c r="C77" s="158"/>
+      <c r="D77" s="155"/>
       <c r="E77" s="83" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F77" s="84">
         <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="141"/>
-      <c r="B78" s="142"/>
-      <c r="C78" s="152"/>
-      <c r="D78" s="149"/>
+      <c r="A78" s="126"/>
+      <c r="B78" s="128"/>
+      <c r="C78" s="159"/>
+      <c r="D78" s="156"/>
       <c r="E78" s="85" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F78" s="86">
         <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="117" t="s">
+      <c r="A79" s="125" t="s">
+        <v>400</v>
+      </c>
+      <c r="B79" s="127" t="s">
+        <v>401</v>
+      </c>
+      <c r="C79" s="127" t="s">
         <v>402</v>
       </c>
-      <c r="B79" s="119" t="s">
+      <c r="D79" s="154" t="s">
         <v>403</v>
       </c>
-      <c r="C79" s="119" t="s">
+      <c r="E79" s="87" t="s">
         <v>404</v>
-      </c>
-      <c r="D79" s="147" t="s">
-        <v>405</v>
-      </c>
-      <c r="E79" s="87" t="s">
-        <v>406</v>
       </c>
       <c r="F79" s="88">
         <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="118"/>
-      <c r="B80" s="120"/>
-      <c r="C80" s="120"/>
-      <c r="D80" s="148"/>
+      <c r="A80" s="152"/>
+      <c r="B80" s="153"/>
+      <c r="C80" s="153"/>
+      <c r="D80" s="155"/>
       <c r="E80" s="83"/>
       <c r="F80" s="89"/>
     </row>
     <row r="81" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="141"/>
-      <c r="B81" s="142"/>
-      <c r="C81" s="142"/>
-      <c r="D81" s="149"/>
+      <c r="A81" s="126"/>
+      <c r="B81" s="128"/>
+      <c r="C81" s="128"/>
+      <c r="D81" s="156"/>
       <c r="E81" s="85"/>
       <c r="F81" s="90"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="153" t="s">
+      <c r="A82" s="135" t="s">
+        <v>405</v>
+      </c>
+      <c r="B82" s="139" t="s">
+        <v>406</v>
+      </c>
+      <c r="C82" s="149">
+        <v>0</v>
+      </c>
+      <c r="D82" s="149" t="s">
         <v>407</v>
       </c>
-      <c r="B82" s="155" t="s">
+      <c r="E82" s="96" t="s">
         <v>408</v>
-      </c>
-      <c r="C82" s="157">
-        <v>0</v>
-      </c>
-      <c r="D82" s="157" t="s">
-        <v>409</v>
-      </c>
-      <c r="E82" s="96" t="s">
-        <v>410</v>
       </c>
       <c r="F82" s="97">
         <v>98</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="154"/>
-      <c r="B83" s="156"/>
-      <c r="C83" s="158"/>
-      <c r="D83" s="158"/>
+      <c r="A83" s="147"/>
+      <c r="B83" s="148"/>
+      <c r="C83" s="150"/>
+      <c r="D83" s="150"/>
       <c r="E83" s="98"/>
       <c r="F83" s="99"/>
       <c r="G83" s="55"/>
     </row>
     <row r="84" spans="1:7" s="56" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="154"/>
-      <c r="B84" s="156"/>
-      <c r="C84" s="158"/>
-      <c r="D84" s="158"/>
+      <c r="A84" s="147"/>
+      <c r="B84" s="148"/>
+      <c r="C84" s="150"/>
+      <c r="D84" s="150"/>
       <c r="E84" s="98" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F84" s="99">
         <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="154"/>
-      <c r="B85" s="156"/>
-      <c r="C85" s="158"/>
-      <c r="D85" s="158"/>
+      <c r="A85" s="147"/>
+      <c r="B85" s="148"/>
+      <c r="C85" s="150"/>
+      <c r="D85" s="150"/>
       <c r="E85" s="98" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F85" s="99">
         <v>111.32</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="154"/>
-      <c r="B86" s="156"/>
-      <c r="C86" s="158"/>
-      <c r="D86" s="159"/>
+      <c r="A86" s="147"/>
+      <c r="B86" s="148"/>
+      <c r="C86" s="150"/>
+      <c r="D86" s="151"/>
       <c r="E86" s="100" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F86" s="101">
         <v>112.2</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="43.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="136" t="s">
+      <c r="A87" s="143" t="s">
+        <v>412</v>
+      </c>
+      <c r="B87" s="143" t="s">
+        <v>413</v>
+      </c>
+      <c r="C87" s="145">
+        <v>0</v>
+      </c>
+      <c r="D87" s="145" t="s">
         <v>414</v>
       </c>
-      <c r="B87" s="136" t="s">
+      <c r="E87" s="57" t="s">
         <v>415</v>
-      </c>
-      <c r="C87" s="134">
-        <v>0</v>
-      </c>
-      <c r="D87" s="134" t="s">
-        <v>416</v>
-      </c>
-      <c r="E87" s="57" t="s">
-        <v>417</v>
       </c>
       <c r="F87" s="58">
         <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A88" s="137"/>
-      <c r="B88" s="137"/>
-      <c r="C88" s="138"/>
-      <c r="D88" s="138"/>
+      <c r="A88" s="144"/>
+      <c r="B88" s="144"/>
+      <c r="C88" s="146"/>
+      <c r="D88" s="146"/>
       <c r="E88" s="59" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F88" s="60">
         <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A89" s="137"/>
-      <c r="B89" s="137"/>
-      <c r="C89" s="138"/>
-      <c r="D89" s="138"/>
+      <c r="A89" s="144"/>
+      <c r="B89" s="144"/>
+      <c r="C89" s="146"/>
+      <c r="D89" s="146"/>
       <c r="E89" s="59"/>
       <c r="F89" s="60"/>
     </row>
     <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A90" s="137"/>
-      <c r="B90" s="137"/>
-      <c r="C90" s="138"/>
-      <c r="D90" s="138"/>
+      <c r="A90" s="144"/>
+      <c r="B90" s="144"/>
+      <c r="C90" s="146"/>
+      <c r="D90" s="146"/>
       <c r="E90" s="61" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F90" s="62">
         <v>28.4</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="137"/>
-      <c r="B91" s="137"/>
-      <c r="C91" s="138"/>
-      <c r="D91" s="138"/>
+      <c r="A91" s="144"/>
+      <c r="B91" s="144"/>
+      <c r="C91" s="146"/>
+      <c r="D91" s="146"/>
       <c r="E91" s="61"/>
       <c r="F91" s="62"/>
     </row>
     <row r="92" spans="1:7" ht="94" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A92" s="63" t="s">
+        <v>423</v>
+      </c>
+      <c r="B92" s="64" t="s">
+        <v>424</v>
+      </c>
+      <c r="C92" s="64" t="s">
         <v>425</v>
       </c>
-      <c r="B92" s="64" t="s">
+      <c r="D92" s="69" t="s">
         <v>426</v>
       </c>
-      <c r="C92" s="64" t="s">
+      <c r="E92" s="70" t="s">
         <v>427</v>
       </c>
-      <c r="D92" s="69" t="s">
+      <c r="F92" s="71"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="125" t="s">
         <v>428</v>
       </c>
-      <c r="E92" s="70" t="s">
+      <c r="B93" s="127" t="s">
         <v>429</v>
       </c>
-      <c r="F92" s="71"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="117" t="s">
+      <c r="C93" s="127" t="s">
         <v>430</v>
       </c>
-      <c r="B93" s="119" t="s">
+      <c r="D93" s="127" t="s">
         <v>431</v>
       </c>
-      <c r="C93" s="119" t="s">
+      <c r="E93" s="121" t="s">
         <v>432</v>
       </c>
-      <c r="D93" s="119" t="s">
+      <c r="F93" s="122"/>
+    </row>
+    <row r="94" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="126"/>
+      <c r="B94" s="128"/>
+      <c r="C94" s="128"/>
+      <c r="D94" s="128"/>
+      <c r="E94" s="123"/>
+      <c r="F94" s="124"/>
+    </row>
+    <row r="95" spans="1:7" ht="29.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="125" t="s">
         <v>433</v>
       </c>
-      <c r="E93" s="172" t="s">
+      <c r="B95" s="127" t="s">
         <v>434</v>
       </c>
-      <c r="F93" s="173"/>
-    </row>
-    <row r="94" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="141"/>
-      <c r="B94" s="142"/>
-      <c r="C94" s="142"/>
-      <c r="D94" s="142"/>
-      <c r="E94" s="174"/>
-      <c r="F94" s="175"/>
-    </row>
-    <row r="95" spans="1:7" ht="29.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="117" t="s">
+      <c r="C95" s="127" t="s">
         <v>435</v>
       </c>
-      <c r="B95" s="119" t="s">
+      <c r="D95" s="127" t="s">
         <v>436</v>
       </c>
-      <c r="C95" s="119" t="s">
+      <c r="E95" s="72" t="s">
         <v>437</v>
       </c>
-      <c r="D95" s="119" t="s">
+      <c r="F95" s="73"/>
+    </row>
+    <row r="96" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="126"/>
+      <c r="B96" s="128"/>
+      <c r="C96" s="128"/>
+      <c r="D96" s="128"/>
+      <c r="E96" s="74" t="s">
         <v>438</v>
-      </c>
-      <c r="E95" s="72" t="s">
-        <v>439</v>
-      </c>
-      <c r="F95" s="73"/>
-    </row>
-    <row r="96" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="141"/>
-      <c r="B96" s="142"/>
-      <c r="C96" s="142"/>
-      <c r="D96" s="142"/>
-      <c r="E96" s="74" t="s">
-        <v>440</v>
       </c>
       <c r="F96" s="75"/>
     </row>
     <row r="97" spans="1:6" ht="49" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="102" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C97" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="D97" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="E97" s="103" t="s">
         <v>315</v>
       </c>
-      <c r="D97" s="28" t="s">
-        <v>441</v>
-      </c>
-      <c r="E97" s="103" t="s">
-        <v>317</v>
-      </c>
       <c r="F97" s="103" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="43.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="153" t="s">
-        <v>420</v>
-      </c>
-      <c r="B98" s="167" t="s">
-        <v>325</v>
-      </c>
-      <c r="C98" s="155">
-        <v>0</v>
-      </c>
-      <c r="D98" s="170">
+      <c r="A98" s="135" t="s">
+        <v>418</v>
+      </c>
+      <c r="B98" s="137" t="s">
+        <v>323</v>
+      </c>
+      <c r="C98" s="139">
+        <v>0</v>
+      </c>
+      <c r="D98" s="141">
         <v>100</v>
       </c>
       <c r="E98" s="57" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F98" s="58">
         <v>131</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="166"/>
-      <c r="B99" s="168"/>
-      <c r="C99" s="169"/>
-      <c r="D99" s="171"/>
+      <c r="A99" s="136"/>
+      <c r="B99" s="138"/>
+      <c r="C99" s="140"/>
+      <c r="D99" s="142"/>
       <c r="E99" s="65"/>
       <c r="F99" s="66"/>
     </row>
     <row r="100" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="160" t="s">
-        <v>422</v>
-      </c>
-      <c r="B100" s="160" t="s">
-        <v>423</v>
-      </c>
-      <c r="C100" s="162">
-        <v>0</v>
-      </c>
-      <c r="D100" s="164">
+      <c r="A100" s="129" t="s">
+        <v>420</v>
+      </c>
+      <c r="B100" s="129" t="s">
+        <v>421</v>
+      </c>
+      <c r="C100" s="131">
+        <v>0</v>
+      </c>
+      <c r="D100" s="133">
         <v>50</v>
       </c>
       <c r="E100" s="57"/>
       <c r="F100" s="58"/>
     </row>
     <row r="101" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="161"/>
-      <c r="B101" s="161"/>
-      <c r="C101" s="163"/>
-      <c r="D101" s="165"/>
+      <c r="A101" s="130"/>
+      <c r="B101" s="130"/>
+      <c r="C101" s="132"/>
+      <c r="D101" s="134"/>
       <c r="E101" s="67" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F101" s="68">
         <v>98</v>
@@ -7831,7 +7831,7 @@
     </row>
     <row r="103" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="B103" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -7842,6 +7842,52 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="B40:B64"/>
+    <mergeCell ref="C40:C64"/>
+    <mergeCell ref="D40:D64"/>
+    <mergeCell ref="A9:A39"/>
+    <mergeCell ref="B9:B39"/>
+    <mergeCell ref="C9:C39"/>
+    <mergeCell ref="D9:D39"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="A66:A75"/>
+    <mergeCell ref="B66:B75"/>
+    <mergeCell ref="C66:C75"/>
+    <mergeCell ref="D66:D75"/>
+    <mergeCell ref="A79:A81"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="D79:D81"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="A87:A91"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="D87:D91"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="D98:D99"/>
     <mergeCell ref="E93:F94"/>
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="B95:B96"/>
@@ -7851,52 +7897,6 @@
     <mergeCell ref="B93:B94"/>
     <mergeCell ref="C93:C94"/>
     <mergeCell ref="D93:D94"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="A87:A91"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="D87:D91"/>
-    <mergeCell ref="A82:A86"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="A79:A81"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="A66:A75"/>
-    <mergeCell ref="B66:B75"/>
-    <mergeCell ref="C66:C75"/>
-    <mergeCell ref="D66:D75"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="B40:B64"/>
-    <mergeCell ref="C40:C64"/>
-    <mergeCell ref="D40:D64"/>
-    <mergeCell ref="A9:A39"/>
-    <mergeCell ref="B9:B39"/>
-    <mergeCell ref="C9:C39"/>
-    <mergeCell ref="D9:D39"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7914,168 +7914,168 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="176" t="s">
-        <v>521</v>
-      </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
+      <c r="A1" s="110" t="s">
+        <v>519</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
     </row>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="106" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C2" s="106" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A3" s="179" t="s">
-        <v>494</v>
-      </c>
-      <c r="B3" s="179"/>
-      <c r="C3" s="179"/>
+      <c r="A3" s="113" t="s">
+        <v>492</v>
+      </c>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="108" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B4" s="108" t="s">
-        <v>496</v>
-      </c>
-      <c r="C4" s="177" t="s">
-        <v>518</v>
+        <v>494</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="108" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B5" s="108" t="s">
-        <v>497</v>
-      </c>
-      <c r="C5" s="178"/>
+        <v>495</v>
+      </c>
+      <c r="C5" s="112"/>
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="108" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B6" s="108" t="s">
-        <v>498</v>
-      </c>
-      <c r="C6" s="178"/>
+        <v>496</v>
+      </c>
+      <c r="C6" s="112"/>
     </row>
     <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="108" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B7" s="108" t="s">
-        <v>499</v>
-      </c>
-      <c r="C7" s="178"/>
+        <v>497</v>
+      </c>
+      <c r="C7" s="112"/>
     </row>
     <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="108" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B8" s="108" t="s">
-        <v>500</v>
-      </c>
-      <c r="C8" s="178"/>
+        <v>498</v>
+      </c>
+      <c r="C8" s="112"/>
     </row>
     <row r="9" spans="1:3" ht="38" x14ac:dyDescent="0.2">
       <c r="A9" s="108" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B9" s="109" t="s">
-        <v>504</v>
-      </c>
-      <c r="C9" s="178"/>
+        <v>502</v>
+      </c>
+      <c r="C9" s="112"/>
     </row>
     <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="108" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>505</v>
-      </c>
-      <c r="C10" s="178"/>
+        <v>503</v>
+      </c>
+      <c r="C10" s="112"/>
     </row>
     <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="108" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B11" s="108" t="s">
-        <v>502</v>
-      </c>
-      <c r="C11" s="178"/>
+        <v>500</v>
+      </c>
+      <c r="C11" s="112"/>
     </row>
     <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="108" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B12" s="108" t="s">
-        <v>506</v>
-      </c>
-      <c r="C12" s="178"/>
+        <v>504</v>
+      </c>
+      <c r="C12" s="112"/>
     </row>
     <row r="13" spans="1:3" ht="57" x14ac:dyDescent="0.2">
       <c r="A13" s="108" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B13" s="109" t="s">
-        <v>507</v>
-      </c>
-      <c r="C13" s="178"/>
+        <v>505</v>
+      </c>
+      <c r="C13" s="112"/>
     </row>
     <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A14" s="179" t="s">
-        <v>508</v>
-      </c>
-      <c r="B14" s="179"/>
-      <c r="C14" s="179"/>
+      <c r="A14" s="113" t="s">
+        <v>506</v>
+      </c>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
     </row>
     <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="108" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B15" s="108" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C15" s="107" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="57" x14ac:dyDescent="0.2">
       <c r="A16" s="108" t="s">
+        <v>508</v>
+      </c>
+      <c r="B16" s="109" t="s">
         <v>510</v>
       </c>
-      <c r="B16" s="109" t="s">
-        <v>512</v>
-      </c>
-      <c r="C16" s="177" t="s">
-        <v>517</v>
+      <c r="C16" s="111" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="38" x14ac:dyDescent="0.2">
       <c r="A17" s="108" t="s">
+        <v>509</v>
+      </c>
+      <c r="B17" s="109" t="s">
         <v>511</v>
       </c>
-      <c r="B17" s="109" t="s">
-        <v>513</v>
-      </c>
-      <c r="C17" s="178"/>
+      <c r="C17" s="112"/>
     </row>
     <row r="18" spans="1:3" ht="38" x14ac:dyDescent="0.2">
       <c r="A18" s="108" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B18" s="109" t="s">
-        <v>515</v>
-      </c>
-      <c r="C18" s="178"/>
+        <v>513</v>
+      </c>
+      <c r="C18" s="112"/>
     </row>
     <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="107"/>
@@ -8084,14 +8084,14 @@
     </row>
     <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="107" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B20" s="107"/>
       <c r="C20" s="107"/>
     </row>
     <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="107" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B21" s="107"/>
       <c r="C21" s="107"/>
@@ -8144,7 +8144,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -8156,7 +8156,7 @@
         <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -8169,13 +8169,13 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="H2" s="110" t="s">
-        <v>255</v>
+      <c r="H2" s="114" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>16</v>
@@ -8195,11 +8195,11 @@
       <c r="G3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="110"/>
+      <c r="H3" s="114"/>
     </row>
     <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>18</v>
@@ -8219,11 +8219,11 @@
       <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="110"/>
+      <c r="H4" s="114"/>
     </row>
     <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>19</v>
@@ -8243,11 +8243,11 @@
       <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="110"/>
+      <c r="H5" s="114"/>
     </row>
     <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>20</v>
@@ -8267,17 +8267,17 @@
       <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="110"/>
+      <c r="H6" s="114"/>
     </row>
     <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D7" s="8">
         <v>0</v>
@@ -8291,17 +8291,17 @@
       <c r="G7" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="110"/>
+      <c r="H7" s="114"/>
     </row>
     <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D8" s="8">
         <v>0</v>
@@ -8315,11 +8315,11 @@
       <c r="G8" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="110"/>
+      <c r="H8" s="114"/>
     </row>
     <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>6</v>
@@ -8339,7 +8339,7 @@
       <c r="G9" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="110"/>
+      <c r="H9" s="114"/>
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -8363,7 +8363,7 @@
       <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="110"/>
+      <c r="H10" s="114"/>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -8385,9 +8385,9 @@
         <v>84</v>
       </c>
       <c r="G11" t="s">
-        <v>134</v>
-      </c>
-      <c r="H11" s="110"/>
+        <v>132</v>
+      </c>
+      <c r="H11" s="114"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
@@ -8399,11 +8399,11 @@
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
-      <c r="H12" s="110"/>
+      <c r="H12" s="114"/>
     </row>
     <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>9</v>
@@ -8423,7 +8423,7 @@
       <c r="G13" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="110"/>
+      <c r="H13" s="114"/>
     </row>
     <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -8447,17 +8447,17 @@
       <c r="G14" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="110"/>
+      <c r="H14" s="114"/>
     </row>
     <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15" s="8">
         <v>0</v>
@@ -8471,17 +8471,17 @@
       <c r="G15" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="110"/>
+      <c r="H15" s="114"/>
     </row>
     <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D16" s="8">
         <v>0</v>
@@ -8495,14 +8495,14 @@
       <c r="G16" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="110"/>
+      <c r="H16" s="114"/>
     </row>
     <row r="17" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="9"/>
     </row>
     <row r="18" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="C18" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -8513,12 +8513,12 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -8560,13 +8560,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -8574,7 +8574,7 @@
         <v>52</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>76</v>
@@ -8586,8 +8586,8 @@
         <v>63</v>
       </c>
       <c r="F2" s="20"/>
-      <c r="G2" s="112" t="s">
-        <v>255</v>
+      <c r="G2" s="116" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -8595,7 +8595,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>77</v>
@@ -8607,14 +8607,14 @@
         <v>64</v>
       </c>
       <c r="F3" s="20"/>
-      <c r="G3" s="112"/>
+      <c r="G3" s="116"/>
     </row>
     <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>53</v>
@@ -8623,20 +8623,20 @@
         <v>0</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F4" s="21"/>
-      <c r="G4" s="112"/>
+      <c r="G4" s="116"/>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>80</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D5" s="20">
         <v>0</v>
@@ -8645,7 +8645,7 @@
         <v>65</v>
       </c>
       <c r="F5" s="20"/>
-      <c r="G5" s="112"/>
+      <c r="G5" s="116"/>
     </row>
     <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -8664,7 +8664,7 @@
         <v>250</v>
       </c>
       <c r="F6" s="20"/>
-      <c r="G6" s="112"/>
+      <c r="G6" s="116"/>
     </row>
     <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -8683,14 +8683,14 @@
         <v>69</v>
       </c>
       <c r="F7" s="20"/>
-      <c r="G7" s="112"/>
+      <c r="G7" s="116"/>
     </row>
     <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>79</v>
@@ -8702,14 +8702,14 @@
         <v>0</v>
       </c>
       <c r="F8" s="20"/>
-      <c r="G8" s="112"/>
+      <c r="G8" s="116"/>
     </row>
     <row r="9" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>81</v>
@@ -8721,18 +8721,18 @@
         <v>0</v>
       </c>
       <c r="F9" s="20"/>
-      <c r="G9" s="112"/>
+      <c r="G9" s="116"/>
     </row>
     <row r="10" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="G10" s="112"/>
+        <v>462</v>
+      </c>
+      <c r="G10" s="116"/>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -8742,7 +8742,7 @@
         <v>100</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>70</v>
@@ -8751,7 +8751,7 @@
         <v>71</v>
       </c>
       <c r="F11" s="20"/>
-      <c r="G11" s="112"/>
+      <c r="G11" s="116"/>
     </row>
     <row r="12" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -8764,13 +8764,13 @@
         <v>83</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F12" s="21"/>
-      <c r="G12" s="112"/>
+      <c r="G12" s="116"/>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -8778,7 +8778,7 @@
     </row>
     <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -8790,13 +8790,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:8" s="113" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="113" t="s">
-        <v>493</v>
+    <row r="16" spans="1:8" s="117" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="117" t="s">
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -8832,21 +8832,21 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>76</v>
@@ -8857,8 +8857,8 @@
       <c r="E2" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="112" t="s">
-        <v>255</v>
+      <c r="F2" s="116" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -8866,7 +8866,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>77</v>
@@ -8877,14 +8877,14 @@
       <c r="E3" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="112"/>
+      <c r="F3" s="116"/>
     </row>
     <row r="4" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>81</v>
@@ -8895,14 +8895,14 @@
       <c r="E4" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="112"/>
+      <c r="F4" s="116"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
         <v>53</v>
@@ -8911,13 +8911,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="F5" s="112"/>
+        <v>127</v>
+      </c>
+      <c r="F5" s="116"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>100</v>
@@ -8931,22 +8931,22 @@
       <c r="E6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="112"/>
+      <c r="F6" s="116"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="112"/>
+      <c r="F7" s="116"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -8964,7 +8964,7 @@
       <c r="E8" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="112"/>
+      <c r="F8" s="116"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -8982,7 +8982,7 @@
       <c r="E9" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="116"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -9000,14 +9000,14 @@
       <c r="E10" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="112"/>
+      <c r="F10" s="116"/>
     </row>
     <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="F11" s="112"/>
+      <c r="F11" s="116"/>
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
@@ -9018,12 +9018,12 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -9059,157 +9059,157 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>468</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>108</v>
-      </c>
       <c r="E2" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" s="112" t="s">
-        <v>255</v>
+        <v>107</v>
+      </c>
+      <c r="F2" s="116" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>76</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="112"/>
+        <v>107</v>
+      </c>
+      <c r="F3" s="116"/>
     </row>
     <row r="4" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" s="112"/>
+        <v>107</v>
+      </c>
+      <c r="F4" s="116"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B5" t="s">
         <v>100</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="112"/>
+        <v>107</v>
+      </c>
+      <c r="F5" s="116"/>
     </row>
     <row r="6" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="112"/>
+        <v>107</v>
+      </c>
+      <c r="F6" s="116"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" s="112"/>
+        <v>106</v>
+      </c>
+      <c r="F7" s="116"/>
     </row>
     <row r="8" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>54</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>81</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="112"/>
+        <v>106</v>
+      </c>
+      <c r="F8" s="116"/>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="F9" s="112"/>
+        <v>106</v>
+      </c>
+      <c r="F9" s="116"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
@@ -9217,7 +9217,7 @@
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C11" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D11" s="4">
         <v>8</v>
@@ -9228,18 +9228,18 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:6" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="114" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="113" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="113" t="s">
-        <v>492</v>
+    <row r="13" spans="1:6" s="118" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="118" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="117" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="117" t="s">
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -9281,157 +9281,157 @@
         <v>1</v>
       </c>
       <c r="D1" s="105" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E1" s="105" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F1" s="104" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>479</v>
-      </c>
       <c r="E6" s="20" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -9440,16 +9440,16 @@
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -9462,7 +9462,7 @@
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D12" s="20">
         <v>0</v>
@@ -9473,17 +9473,17 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="115" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="115" t="s">
-        <v>490</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="119" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="119" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -9523,24 +9523,24 @@
         <v>1</v>
       </c>
       <c r="D1" s="105" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E1" s="105" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
         <v>90</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>103</v>
@@ -9548,19 +9548,19 @@
       <c r="E2" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="112" t="s">
-        <v>255</v>
+      <c r="F2" s="116" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>103</v>
@@ -9568,17 +9568,17 @@
       <c r="E3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="112"/>
+      <c r="F3" s="116"/>
     </row>
     <row r="4" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>96</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>103</v>
@@ -9586,17 +9586,17 @@
       <c r="E4" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="112"/>
+      <c r="F4" s="116"/>
     </row>
     <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>103</v>
@@ -9604,11 +9604,11 @@
       <c r="E5" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="112"/>
+      <c r="F5" s="116"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B6" t="s">
         <v>98</v>
@@ -9622,7 +9622,7 @@
       <c r="E6" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F6" s="112"/>
+      <c r="F6" s="116"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -9632,7 +9632,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>103</v>
@@ -9640,17 +9640,17 @@
       <c r="E7" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="112"/>
+      <c r="F7" s="116"/>
     </row>
     <row r="8" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>87</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>102</v>
@@ -9658,17 +9658,17 @@
       <c r="E8" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F8" s="112"/>
+      <c r="F8" s="116"/>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B9" t="s">
         <v>100</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>103</v>
@@ -9676,7 +9676,7 @@
       <c r="E9" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="116"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -9689,12 +9689,12 @@
         <v>15</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>104</v>
+        <v>520</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10" s="112"/>
+        <v>521</v>
+      </c>
+      <c r="F10" s="116"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
@@ -9713,19 +9713,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:6" s="113" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="113" t="s">
-        <v>492</v>
+    <row r="15" spans="1:6" s="117" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="117" t="s">
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -9766,33 +9766,33 @@
         <v>1</v>
       </c>
       <c r="D1" s="105" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E1" s="105" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>270</v>
-      </c>
       <c r="D2" s="20" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="F2" s="112" t="s">
-        <v>465</v>
+        <v>284</v>
+      </c>
+      <c r="F2" s="116" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -9800,36 +9800,36 @@
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="112"/>
+      <c r="F3" s="116"/>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="112"/>
+      <c r="F4" s="116"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
@@ -9839,51 +9839,51 @@
         <v>91</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F5" s="112"/>
+        <v>260</v>
+      </c>
+      <c r="F5" s="116"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="112"/>
+        <v>260</v>
+      </c>
+      <c r="F6" s="116"/>
     </row>
     <row r="7" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F7" s="112"/>
+        <v>260</v>
+      </c>
+      <c r="F7" s="116"/>
     </row>
     <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -9893,87 +9893,87 @@
         <v>101</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="F8" s="112"/>
+        <v>242</v>
+      </c>
+      <c r="F8" s="116"/>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="F9" s="112"/>
+        <v>279</v>
+      </c>
+      <c r="F9" s="116"/>
     </row>
     <row r="10" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="F10" s="112"/>
+        <v>280</v>
+      </c>
+      <c r="F10" s="116"/>
     </row>
     <row r="11" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="F11" s="112"/>
+        <v>264</v>
+      </c>
+      <c r="F11" s="116"/>
     </row>
     <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>87</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="F12" s="112"/>
+        <v>264</v>
+      </c>
+      <c r="F12" s="116"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="9"/>
@@ -9981,7 +9981,7 @@
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -9992,12 +9992,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="116" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="116" t="s">
-        <v>260</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="120" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="120" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -10043,30 +10043,30 @@
         <v>51</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>270</v>
-      </c>
       <c r="D2" s="20">
         <v>0</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="F2" s="112" t="s">
-        <v>465</v>
+        <v>284</v>
+      </c>
+      <c r="F2" s="116" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -10074,10 +10074,10 @@
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D3" s="20">
         <v>0</v>
@@ -10085,17 +10085,17 @@
       <c r="E3" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="112"/>
+      <c r="F3" s="116"/>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D4" s="20">
         <v>0</v>
@@ -10103,7 +10103,7 @@
       <c r="E4" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="112"/>
+      <c r="F4" s="116"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
@@ -10113,51 +10113,51 @@
         <v>91</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D5" s="20">
         <v>0</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F5" s="112"/>
+        <v>260</v>
+      </c>
+      <c r="F5" s="116"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D6" s="20">
         <v>0</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="112"/>
+        <v>260</v>
+      </c>
+      <c r="F6" s="116"/>
     </row>
     <row r="7" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D7" s="20">
         <v>0</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F7" s="112"/>
+        <v>260</v>
+      </c>
+      <c r="F7" s="116"/>
     </row>
     <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -10167,87 +10167,87 @@
         <v>101</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D8" s="20">
         <v>0</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="F8" s="112"/>
+        <v>242</v>
+      </c>
+      <c r="F8" s="116"/>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E9" s="20">
         <v>0</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="116"/>
     </row>
     <row r="10" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E10" s="20">
         <v>0</v>
       </c>
-      <c r="F10" s="112"/>
+      <c r="F10" s="116"/>
     </row>
     <row r="11" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E11" s="20">
         <v>0</v>
       </c>
-      <c r="F11" s="112"/>
+      <c r="F11" s="116"/>
     </row>
     <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>87</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E12" s="20">
         <v>0</v>
       </c>
-      <c r="F12" s="112"/>
+      <c r="F12" s="116"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
@@ -10256,7 +10256,7 @@
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -10267,12 +10267,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="116" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="116" t="s">
-        <v>260</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="120" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="120" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
